--- a/#Hearts2Hearts_anonymized.xlsx
+++ b/#Hearts2Hearts_anonymized.xlsx
@@ -446,17 +446,17 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>关注的userName</t>
+          <t>followed_userName</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>粉丝的userName</t>
+          <t>follower_userName</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>发文量</t>
+          <t>Number of Publications</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -483,12 +483,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>user_00850</t>
+          <t>user_00863</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>user_00854</t>
+          <t>user_00867</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -499,7 +499,7 @@
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>user_00869</t>
+          <t>user_00882</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -525,12 +525,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>user_00850</t>
+          <t>user_00863</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>user_00854</t>
+          <t>user_00867</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -541,7 +541,7 @@
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>user_00869</t>
+          <t>user_00882</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -567,12 +567,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>user_00850</t>
+          <t>user_00863</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>user_00854</t>
+          <t>user_00867</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -583,7 +583,7 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>user_00869</t>
+          <t>user_00882</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -609,12 +609,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>user_00850</t>
+          <t>user_00863</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>user_00854</t>
+          <t>user_00867</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -625,7 +625,7 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>user_00869</t>
+          <t>user_00882</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -651,12 +651,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>user_00850</t>
+          <t>user_00863</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>user_00854</t>
+          <t>user_00867</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -667,7 +667,7 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>user_00869</t>
+          <t>user_00882</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -693,12 +693,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>user_00850</t>
+          <t>user_00863</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>user_00854</t>
+          <t>user_00867</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -709,7 +709,7 @@
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>user_00869</t>
+          <t>user_00882</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -735,12 +735,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>user_00850</t>
+          <t>user_00863</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>user_00854</t>
+          <t>user_00867</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -751,7 +751,7 @@
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>user_00869</t>
+          <t>user_00882</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -777,12 +777,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>user_00869</t>
+          <t>user_00882</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>user_02766</t>
+          <t>user_02829</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>user_02295</t>
+          <t>user_02328</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -825,12 +825,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>user_00869</t>
+          <t>user_00882</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>user_02766</t>
+          <t>user_02829</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>user_02295</t>
+          <t>user_02328</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
@@ -869,12 +869,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>user_00869</t>
+          <t>user_00882</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>user_02766</t>
+          <t>user_02829</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>user_02295</t>
+          <t>user_02328</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
@@ -913,12 +913,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>user_00869</t>
+          <t>user_00882</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>user_02766</t>
+          <t>user_02829</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>user_02295</t>
+          <t>user_02328</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
@@ -957,12 +957,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>user_00869</t>
+          <t>user_00882</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>user_02766</t>
+          <t>user_02829</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>user_02295</t>
+          <t>user_02328</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
@@ -1001,12 +1001,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>user_00869</t>
+          <t>user_00882</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>user_02766</t>
+          <t>user_02829</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1016,7 +1016,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>user_02295</t>
+          <t>user_02328</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -1045,12 +1045,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>user_00869</t>
+          <t>user_00882</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>user_02766</t>
+          <t>user_02829</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>user_02295</t>
+          <t>user_02328</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -1089,12 +1089,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>user_02295</t>
+          <t>user_02328</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>user_02792</t>
+          <t>user_02856</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>user_02661</t>
+          <t>user_02721</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -1134,12 +1134,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>user_02295</t>
+          <t>user_02328</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>user_02792</t>
+          <t>user_02856</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>user_02661</t>
+          <t>user_02721</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -1179,12 +1179,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>user_02295</t>
+          <t>user_02328</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>user_02792</t>
+          <t>user_02856</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>user_02661</t>
+          <t>user_02721</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
@@ -1225,12 +1225,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>user_02295</t>
+          <t>user_02328</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>user_02792</t>
+          <t>user_02856</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>user_02661</t>
+          <t>user_02721</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
@@ -1268,12 +1268,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>user_02295</t>
+          <t>user_02328</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>user_02792</t>
+          <t>user_02856</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>user_02661</t>
+          <t>user_02721</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
@@ -1311,12 +1311,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>user_02295</t>
+          <t>user_02328</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>user_02792</t>
+          <t>user_02856</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>user_02661</t>
+          <t>user_02721</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
@@ -1355,12 +1355,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>user_02295</t>
+          <t>user_02328</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>user_02792</t>
+          <t>user_02856</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>user_02661</t>
+          <t>user_02721</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
@@ -1398,12 +1398,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>user_02295</t>
+          <t>user_02328</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>user_02792</t>
+          <t>user_02856</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1430,12 +1430,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>user_02295</t>
+          <t>user_02328</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>user_02792</t>
+          <t>user_02856</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1465,12 +1465,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>user_02295</t>
+          <t>user_02328</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>user_02792</t>
+          <t>user_02856</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1498,12 +1498,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>user_02295</t>
+          <t>user_02328</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>user_02792</t>
+          <t>user_02856</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1535,12 +1535,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>user_02295</t>
+          <t>user_02328</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>user_02792</t>
+          <t>user_02856</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1567,12 +1567,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>user_02295</t>
+          <t>user_02328</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>user_02792</t>
+          <t>user_02856</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1599,12 +1599,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>user_02295</t>
+          <t>user_02328</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>user_02792</t>
+          <t>user_02856</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1632,12 +1632,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>user_02295</t>
+          <t>user_02328</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>user_02792</t>
+          <t>user_02856</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1664,12 +1664,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>user_02295</t>
+          <t>user_02328</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>user_02792</t>
+          <t>user_02856</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1704,12 +1704,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>user_02295</t>
+          <t>user_02328</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>user_02792</t>
+          <t>user_02856</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1737,12 +1737,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>user_02295</t>
+          <t>user_02328</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>user_02792</t>
+          <t>user_02856</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1769,12 +1769,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>user_02295</t>
+          <t>user_02328</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>user_02792</t>
+          <t>user_02856</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1802,12 +1802,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>user_02295</t>
+          <t>user_02328</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>user_02792</t>
+          <t>user_02856</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1835,12 +1835,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>user_02295</t>
+          <t>user_02328</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>user_02792</t>
+          <t>user_02856</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1868,12 +1868,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>user_02295</t>
+          <t>user_02328</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>user_02792</t>
+          <t>user_02856</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1902,12 +1902,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>user_02295</t>
+          <t>user_02328</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>user_02792</t>
+          <t>user_02856</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1934,12 +1934,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>user_02295</t>
+          <t>user_02328</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>user_02792</t>
+          <t>user_02856</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1967,12 +1967,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>user_02295</t>
+          <t>user_02328</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>user_02792</t>
+          <t>user_02856</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2004,12 +2004,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>user_02295</t>
+          <t>user_02328</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>user_02792</t>
+          <t>user_02856</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2040,12 +2040,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>user_02295</t>
+          <t>user_02328</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>user_02792</t>
+          <t>user_02856</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2072,12 +2072,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>user_02136</t>
+          <t>user_02160</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>user_01029</t>
+          <t>user_01043</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2088,7 +2088,7 @@
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>user_02792</t>
+          <t>user_02856</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -2110,12 +2110,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>user_02136</t>
+          <t>user_02160</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>user_01029</t>
+          <t>user_01043</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2142,12 +2142,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>user_02136</t>
+          <t>user_02160</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>user_01029</t>
+          <t>user_01043</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2175,12 +2175,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>user_02136</t>
+          <t>user_02160</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>user_01029</t>
+          <t>user_01043</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2208,12 +2208,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>user_02136</t>
+          <t>user_02160</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>user_01029</t>
+          <t>user_01043</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2242,12 +2242,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>user_02136</t>
+          <t>user_02160</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>user_01029</t>
+          <t>user_01043</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2274,12 +2274,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>user_02136</t>
+          <t>user_02160</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>user_01029</t>
+          <t>user_01043</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2309,12 +2309,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>user_02136</t>
+          <t>user_02160</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>user_01029</t>
+          <t>user_01043</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2342,12 +2342,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>user_02136</t>
+          <t>user_02160</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>user_01029</t>
+          <t>user_01043</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2375,12 +2375,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>user_02136</t>
+          <t>user_02160</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>user_01029</t>
+          <t>user_01043</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2411,12 +2411,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>user_02136</t>
+          <t>user_02160</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>user_01029</t>
+          <t>user_01043</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2447,12 +2447,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>user_02136</t>
+          <t>user_02160</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>user_01029</t>
+          <t>user_01043</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2479,12 +2479,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>user_02136</t>
+          <t>user_02160</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>user_01029</t>
+          <t>user_01043</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2516,12 +2516,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>user_02136</t>
+          <t>user_02160</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>user_01029</t>
+          <t>user_01043</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2548,12 +2548,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>user_02136</t>
+          <t>user_02160</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>user_01029</t>
+          <t>user_01043</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2580,12 +2580,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>user_02136</t>
+          <t>user_02160</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>user_01029</t>
+          <t>user_01043</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2613,12 +2613,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>user_01292</t>
+          <t>user_01312</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>user_02181</t>
+          <t>user_02206</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2629,7 +2629,7 @@
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>user_02792</t>
+          <t>user_02856</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -2654,12 +2654,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>user_01292</t>
+          <t>user_01312</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>user_02181</t>
+          <t>user_02206</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2686,12 +2686,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>user_01292</t>
+          <t>user_01312</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>user_02181</t>
+          <t>user_02206</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2718,12 +2718,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>user_01292</t>
+          <t>user_01312</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>user_02181</t>
+          <t>user_02206</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2751,12 +2751,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>user_01292</t>
+          <t>user_01312</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>user_02181</t>
+          <t>user_02206</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2784,12 +2784,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>user_01292</t>
+          <t>user_01312</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>user_02181</t>
+          <t>user_02206</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2817,12 +2817,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>user_01292</t>
+          <t>user_01312</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>user_02181</t>
+          <t>user_02206</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2850,12 +2850,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>user_01292</t>
+          <t>user_01312</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>user_02181</t>
+          <t>user_02206</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2883,12 +2883,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>user_01292</t>
+          <t>user_01312</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>user_02181</t>
+          <t>user_02206</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2916,12 +2916,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>user_01292</t>
+          <t>user_01312</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>user_02181</t>
+          <t>user_02206</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2949,12 +2949,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>user_01292</t>
+          <t>user_01312</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>user_02181</t>
+          <t>user_02206</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2982,12 +2982,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>user_01292</t>
+          <t>user_01312</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>user_02181</t>
+          <t>user_02206</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3016,12 +3016,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>user_01292</t>
+          <t>user_01312</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>user_02181</t>
+          <t>user_02206</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3048,12 +3048,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>user_01292</t>
+          <t>user_01312</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>user_02181</t>
+          <t>user_02206</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3080,12 +3080,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>user_01292</t>
+          <t>user_01312</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>user_02181</t>
+          <t>user_02206</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3112,12 +3112,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>user_01292</t>
+          <t>user_01312</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>user_02181</t>
+          <t>user_02206</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3144,12 +3144,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>user_01292</t>
+          <t>user_01312</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>user_02181</t>
+          <t>user_02206</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3177,12 +3177,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>user_01292</t>
+          <t>user_01312</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>user_02181</t>
+          <t>user_02206</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3209,12 +3209,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>user_01292</t>
+          <t>user_01312</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>user_02181</t>
+          <t>user_02206</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3244,12 +3244,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>user_01292</t>
+          <t>user_01312</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>user_02181</t>
+          <t>user_02206</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3277,12 +3277,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>user_01292</t>
+          <t>user_01312</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>user_02181</t>
+          <t>user_02206</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3311,12 +3311,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>user_02431</t>
+          <t>user_02475</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>user_02746</t>
+          <t>user_02807</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3327,7 +3327,7 @@
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>user_02792</t>
+          <t>user_02856</t>
         </is>
       </c>
       <c r="F80" t="n">
@@ -3350,12 +3350,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>user_02431</t>
+          <t>user_02475</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>user_02746</t>
+          <t>user_02807</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3383,12 +3383,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>user_02431</t>
+          <t>user_02475</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>user_02746</t>
+          <t>user_02807</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3416,12 +3416,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>user_02431</t>
+          <t>user_02475</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>user_02746</t>
+          <t>user_02807</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3450,12 +3450,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>user_02431</t>
+          <t>user_02475</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>user_02746</t>
+          <t>user_02807</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3482,12 +3482,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>user_02431</t>
+          <t>user_02475</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>user_02746</t>
+          <t>user_02807</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3514,12 +3514,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>user_02431</t>
+          <t>user_02475</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>user_02746</t>
+          <t>user_02807</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3546,12 +3546,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>user_02431</t>
+          <t>user_02475</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>user_02746</t>
+          <t>user_02807</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3582,12 +3582,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>user_02431</t>
+          <t>user_02475</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>user_02746</t>
+          <t>user_02807</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3615,12 +3615,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>user_02431</t>
+          <t>user_02475</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>user_02746</t>
+          <t>user_02807</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3648,12 +3648,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>user_02431</t>
+          <t>user_02475</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>user_02746</t>
+          <t>user_02807</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3682,12 +3682,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>user_02431</t>
+          <t>user_02475</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>user_02746</t>
+          <t>user_02807</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3715,12 +3715,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>user_02431</t>
+          <t>user_02475</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>user_02746</t>
+          <t>user_02807</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3747,12 +3747,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>user_02431</t>
+          <t>user_02475</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>user_02746</t>
+          <t>user_02807</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3780,12 +3780,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>user_02431</t>
+          <t>user_02475</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>user_02746</t>
+          <t>user_02807</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3812,12 +3812,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>user_02431</t>
+          <t>user_02475</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>user_02746</t>
+          <t>user_02807</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3845,12 +3845,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>user_02431</t>
+          <t>user_02475</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>user_02746</t>
+          <t>user_02807</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3880,12 +3880,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>user_02431</t>
+          <t>user_02475</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>user_02746</t>
+          <t>user_02807</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3913,12 +3913,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>user_02884</t>
+          <t>user_02955</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>user_02224</t>
+          <t>user_02250</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3929,7 +3929,7 @@
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>user_02792</t>
+          <t>user_02856</t>
         </is>
       </c>
       <c r="F98" t="n">
@@ -3969,7 +3969,7 @@
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>user_02792</t>
+          <t>user_02856</t>
         </is>
       </c>
       <c r="F99" t="n">
@@ -4612,12 +4612,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>user_02933</t>
+          <t>user_03011</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>user_02489</t>
+          <t>user_02537</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4628,7 +4628,7 @@
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr">
         <is>
-          <t>user_02792</t>
+          <t>user_02856</t>
         </is>
       </c>
       <c r="F119" t="n">
@@ -4651,12 +4651,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>user_02685</t>
+          <t>user_02745</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>user_02824</t>
+          <t>user_02889</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4667,7 +4667,7 @@
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr">
         <is>
-          <t>user_02792</t>
+          <t>user_02856</t>
         </is>
       </c>
       <c r="F120" t="n">
@@ -4690,12 +4690,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>user_02685</t>
+          <t>user_02745</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>user_02824</t>
+          <t>user_02889</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4723,12 +4723,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>user_02685</t>
+          <t>user_02745</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>user_02824</t>
+          <t>user_02889</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4758,12 +4758,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>user_02685</t>
+          <t>user_02745</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>user_02824</t>
+          <t>user_02889</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4791,12 +4791,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>user_02685</t>
+          <t>user_02745</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>user_02824</t>
+          <t>user_02889</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4823,12 +4823,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>user_02685</t>
+          <t>user_02745</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>user_02824</t>
+          <t>user_02889</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4859,12 +4859,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>user_02685</t>
+          <t>user_02745</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>user_02824</t>
+          <t>user_02889</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4893,12 +4893,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>user_02685</t>
+          <t>user_02745</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>user_02824</t>
+          <t>user_02889</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4925,12 +4925,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>user_02685</t>
+          <t>user_02745</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>user_02824</t>
+          <t>user_02889</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4958,12 +4958,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>user_02685</t>
+          <t>user_02745</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>user_02824</t>
+          <t>user_02889</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4991,12 +4991,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>user_02685</t>
+          <t>user_02745</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>user_02824</t>
+          <t>user_02889</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -5024,12 +5024,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>user_02685</t>
+          <t>user_02745</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>user_02824</t>
+          <t>user_02889</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -5056,12 +5056,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>user_02685</t>
+          <t>user_02745</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>user_02824</t>
+          <t>user_02889</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -5088,12 +5088,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>user_02685</t>
+          <t>user_02745</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>user_02824</t>
+          <t>user_02889</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -5120,12 +5120,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>user_02685</t>
+          <t>user_02745</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>user_02824</t>
+          <t>user_02889</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -5156,12 +5156,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>user_02685</t>
+          <t>user_02745</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>user_02824</t>
+          <t>user_02889</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -5191,12 +5191,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>user_02685</t>
+          <t>user_02745</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>user_02824</t>
+          <t>user_02889</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -5225,12 +5225,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>user_02685</t>
+          <t>user_02745</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>user_02824</t>
+          <t>user_02889</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -5261,12 +5261,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>user_02685</t>
+          <t>user_02745</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>user_02824</t>
+          <t>user_02889</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5294,12 +5294,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>user_02685</t>
+          <t>user_02745</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>user_02824</t>
+          <t>user_02889</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -5328,12 +5328,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>user_02685</t>
+          <t>user_02745</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>user_02824</t>
+          <t>user_02889</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -5360,12 +5360,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>user_02904</t>
+          <t>user_02975</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>user_02822</t>
+          <t>user_02887</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -5376,7 +5376,7 @@
       <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr">
         <is>
-          <t>user_02792</t>
+          <t>user_02856</t>
         </is>
       </c>
       <c r="F141" t="n">
@@ -5398,12 +5398,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>user_02904</t>
+          <t>user_02975</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>user_02822</t>
+          <t>user_02887</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -5430,12 +5430,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>user_02904</t>
+          <t>user_02975</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>user_02822</t>
+          <t>user_02887</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -5463,12 +5463,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>user_02904</t>
+          <t>user_02975</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>user_02822</t>
+          <t>user_02887</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5495,12 +5495,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>user_02904</t>
+          <t>user_02975</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>user_02822</t>
+          <t>user_02887</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5528,12 +5528,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>user_02904</t>
+          <t>user_02975</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>user_02822</t>
+          <t>user_02887</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5562,12 +5562,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>user_02904</t>
+          <t>user_02975</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>user_02822</t>
+          <t>user_02887</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5594,12 +5594,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>user_02904</t>
+          <t>user_02975</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>user_02822</t>
+          <t>user_02887</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5626,12 +5626,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>user_02904</t>
+          <t>user_02975</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>user_02822</t>
+          <t>user_02887</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5658,12 +5658,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>user_02904</t>
+          <t>user_02975</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>user_02822</t>
+          <t>user_02887</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5690,12 +5690,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>user_02904</t>
+          <t>user_02975</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>user_02822</t>
+          <t>user_02887</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5722,12 +5722,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>user_02904</t>
+          <t>user_02975</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>user_02822</t>
+          <t>user_02887</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -5755,12 +5755,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>user_02904</t>
+          <t>user_02975</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>user_02822</t>
+          <t>user_02887</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5788,12 +5788,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>user_02904</t>
+          <t>user_02975</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>user_02822</t>
+          <t>user_02887</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5820,12 +5820,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>user_02904</t>
+          <t>user_02975</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>user_02822</t>
+          <t>user_02887</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5853,12 +5853,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>user_02904</t>
+          <t>user_02975</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>user_02822</t>
+          <t>user_02887</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -5891,12 +5891,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>user_02904</t>
+          <t>user_02975</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>user_02822</t>
+          <t>user_02887</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5923,12 +5923,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>user_02904</t>
+          <t>user_02975</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>user_02822</t>
+          <t>user_02887</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5957,12 +5957,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>user_02904</t>
+          <t>user_02975</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>user_02822</t>
+          <t>user_02887</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5990,12 +5990,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>user_02904</t>
+          <t>user_02975</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>user_02822</t>
+          <t>user_02887</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -6024,12 +6024,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>user_02904</t>
+          <t>user_02975</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>user_02822</t>
+          <t>user_02887</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -6056,12 +6056,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>user_02957</t>
+          <t>user_03037</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>user_02619</t>
+          <t>user_02675</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -6072,7 +6072,7 @@
       <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr">
         <is>
-          <t>user_02792</t>
+          <t>user_02856</t>
         </is>
       </c>
       <c r="F162" t="n">
@@ -6096,12 +6096,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>user_02957</t>
+          <t>user_03037</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>user_02619</t>
+          <t>user_02675</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -6128,12 +6128,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>user_02957</t>
+          <t>user_03037</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>user_02619</t>
+          <t>user_02675</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -6161,12 +6161,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>user_02957</t>
+          <t>user_03037</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>user_02619</t>
+          <t>user_02675</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -6193,12 +6193,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>user_02957</t>
+          <t>user_03037</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>user_02619</t>
+          <t>user_02675</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -6225,12 +6225,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>user_02957</t>
+          <t>user_03037</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>user_02619</t>
+          <t>user_02675</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -6257,12 +6257,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>user_02957</t>
+          <t>user_03037</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>user_02619</t>
+          <t>user_02675</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -6289,12 +6289,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>user_02957</t>
+          <t>user_03037</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>user_02619</t>
+          <t>user_02675</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -6322,12 +6322,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>user_02957</t>
+          <t>user_03037</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>user_02619</t>
+          <t>user_02675</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -6355,12 +6355,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>user_02957</t>
+          <t>user_03037</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>user_02619</t>
+          <t>user_02675</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -6390,12 +6390,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>user_02957</t>
+          <t>user_03037</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>user_02619</t>
+          <t>user_02675</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -6422,12 +6422,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>user_02957</t>
+          <t>user_03037</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>user_02619</t>
+          <t>user_02675</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -6454,12 +6454,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>user_02957</t>
+          <t>user_03037</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>user_02619</t>
+          <t>user_02675</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -6486,12 +6486,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>user_02957</t>
+          <t>user_03037</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>user_02619</t>
+          <t>user_02675</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -6519,12 +6519,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>user_02957</t>
+          <t>user_03037</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>user_02619</t>
+          <t>user_02675</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -6551,12 +6551,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>user_02957</t>
+          <t>user_03037</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>user_02619</t>
+          <t>user_02675</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -6584,12 +6584,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>user_02804</t>
+          <t>user_02868</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>user_02540</t>
+          <t>user_02591</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -6600,7 +6600,7 @@
       <c r="D178" t="inlineStr"/>
       <c r="E178" t="inlineStr">
         <is>
-          <t>user_02792</t>
+          <t>user_02856</t>
         </is>
       </c>
       <c r="F178" t="n">
@@ -6629,12 +6629,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>user_02804</t>
+          <t>user_02868</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>user_02540</t>
+          <t>user_02591</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -6662,12 +6662,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>user_02804</t>
+          <t>user_02868</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>user_02540</t>
+          <t>user_02591</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -6694,12 +6694,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>user_02804</t>
+          <t>user_02868</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>user_02540</t>
+          <t>user_02591</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -6727,12 +6727,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>user_02804</t>
+          <t>user_02868</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>user_02540</t>
+          <t>user_02591</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -6763,12 +6763,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>user_02804</t>
+          <t>user_02868</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>user_02540</t>
+          <t>user_02591</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -6795,12 +6795,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>user_02804</t>
+          <t>user_02868</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>user_02540</t>
+          <t>user_02591</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -6829,12 +6829,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>user_02804</t>
+          <t>user_02868</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>user_02540</t>
+          <t>user_02591</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -6861,12 +6861,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>user_02804</t>
+          <t>user_02868</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>user_02540</t>
+          <t>user_02591</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -6894,12 +6894,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>user_02804</t>
+          <t>user_02868</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>user_02540</t>
+          <t>user_02591</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -6926,12 +6926,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>user_02804</t>
+          <t>user_02868</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>user_02540</t>
+          <t>user_02591</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -6959,12 +6959,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>user_02804</t>
+          <t>user_02868</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>user_02540</t>
+          <t>user_02591</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -6992,12 +6992,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>user_02804</t>
+          <t>user_02868</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>user_02540</t>
+          <t>user_02591</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -7024,12 +7024,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>user_02804</t>
+          <t>user_02868</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>user_02540</t>
+          <t>user_02591</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -7056,12 +7056,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>user_02804</t>
+          <t>user_02868</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>user_02540</t>
+          <t>user_02591</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -7089,12 +7089,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>user_02804</t>
+          <t>user_02868</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>user_02540</t>
+          <t>user_02591</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -7122,12 +7122,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>user_02804</t>
+          <t>user_02868</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>user_02540</t>
+          <t>user_02591</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -7154,12 +7154,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>user_02804</t>
+          <t>user_02868</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>user_02540</t>
+          <t>user_02591</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -7186,12 +7186,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>user_02804</t>
+          <t>user_02868</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>user_02540</t>
+          <t>user_02591</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -7221,12 +7221,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>user_02804</t>
+          <t>user_02868</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>user_02540</t>
+          <t>user_02591</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -7256,12 +7256,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>user_02804</t>
+          <t>user_02868</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>user_02540</t>
+          <t>user_02591</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -7288,12 +7288,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>user_02661</t>
+          <t>user_02721</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>user_02652</t>
+          <t>user_02711</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -7304,7 +7304,7 @@
       <c r="D199" t="inlineStr"/>
       <c r="E199" t="inlineStr">
         <is>
-          <t>user_01529</t>
+          <t>user_01550</t>
         </is>
       </c>
       <c r="F199" t="n">
@@ -7336,12 +7336,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>user_02661</t>
+          <t>user_02721</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>user_02652</t>
+          <t>user_02711</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -7352,7 +7352,7 @@
       <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr">
         <is>
-          <t>user_01529</t>
+          <t>user_01550</t>
         </is>
       </c>
       <c r="F200" t="n">
@@ -7379,12 +7379,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>user_02661</t>
+          <t>user_02721</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>user_02652</t>
+          <t>user_02711</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -7395,7 +7395,7 @@
       <c r="D201" t="inlineStr"/>
       <c r="E201" t="inlineStr">
         <is>
-          <t>user_01529</t>
+          <t>user_01550</t>
         </is>
       </c>
       <c r="F201" t="n">
@@ -7422,12 +7422,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>user_02661</t>
+          <t>user_02721</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>user_02652</t>
+          <t>user_02711</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -7438,7 +7438,7 @@
       <c r="D202" t="inlineStr"/>
       <c r="E202" t="inlineStr">
         <is>
-          <t>user_01529</t>
+          <t>user_01550</t>
         </is>
       </c>
       <c r="F202" t="n">
@@ -7469,12 +7469,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>user_02661</t>
+          <t>user_02721</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>user_02652</t>
+          <t>user_02711</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -7485,7 +7485,7 @@
       <c r="D203" t="inlineStr"/>
       <c r="E203" t="inlineStr">
         <is>
-          <t>user_01529</t>
+          <t>user_01550</t>
         </is>
       </c>
       <c r="F203" t="n">
@@ -7515,12 +7515,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>user_02661</t>
+          <t>user_02721</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>user_02652</t>
+          <t>user_02711</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -7531,7 +7531,7 @@
       <c r="D204" t="inlineStr"/>
       <c r="E204" t="inlineStr">
         <is>
-          <t>user_01529</t>
+          <t>user_01550</t>
         </is>
       </c>
       <c r="F204" t="n">
@@ -7558,12 +7558,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>user_02661</t>
+          <t>user_02721</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>user_02652</t>
+          <t>user_02711</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -7574,7 +7574,7 @@
       <c r="D205" t="inlineStr"/>
       <c r="E205" t="inlineStr">
         <is>
-          <t>user_01529</t>
+          <t>user_01550</t>
         </is>
       </c>
       <c r="F205" t="n">
@@ -7601,12 +7601,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>user_02934</t>
+          <t>user_03012</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>user_02652</t>
+          <t>user_02711</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -7637,12 +7637,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>user_02934</t>
+          <t>user_03012</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>user_02652</t>
+          <t>user_02711</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -7673,12 +7673,12 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>user_02934</t>
+          <t>user_03012</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>user_02652</t>
+          <t>user_02711</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -7705,12 +7705,12 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>user_02934</t>
+          <t>user_03012</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>user_02652</t>
+          <t>user_02711</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -7738,12 +7738,12 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>user_02934</t>
+          <t>user_03012</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>user_02652</t>
+          <t>user_02711</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -7770,12 +7770,12 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>user_02934</t>
+          <t>user_03012</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>user_02652</t>
+          <t>user_02711</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -7802,12 +7802,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>user_02934</t>
+          <t>user_03012</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>user_02652</t>
+          <t>user_02711</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -7834,12 +7834,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>user_02934</t>
+          <t>user_03012</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>user_02652</t>
+          <t>user_02711</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -7866,12 +7866,12 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>user_02934</t>
+          <t>user_03012</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>user_02652</t>
+          <t>user_02711</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -7898,12 +7898,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>user_02934</t>
+          <t>user_03012</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>user_02652</t>
+          <t>user_02711</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -7930,12 +7930,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>user_02934</t>
+          <t>user_03012</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>user_02652</t>
+          <t>user_02711</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -7962,12 +7962,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>user_02934</t>
+          <t>user_03012</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>user_02652</t>
+          <t>user_02711</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -7994,12 +7994,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>user_02934</t>
+          <t>user_03012</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>user_02652</t>
+          <t>user_02711</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -8027,12 +8027,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>user_02920</t>
+          <t>user_02992</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>user_02591</t>
+          <t>user_02644</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -8043,7 +8043,7 @@
       <c r="D219" t="inlineStr"/>
       <c r="E219" t="inlineStr">
         <is>
-          <t>user_02652</t>
+          <t>user_02711</t>
         </is>
       </c>
       <c r="F219" t="n">
@@ -8069,12 +8069,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>user_02920</t>
+          <t>user_02992</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>user_02591</t>
+          <t>user_02644</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -8101,12 +8101,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>user_02920</t>
+          <t>user_02992</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>user_02591</t>
+          <t>user_02644</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -8137,12 +8137,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>user_02920</t>
+          <t>user_02992</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>user_02591</t>
+          <t>user_02644</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -8173,12 +8173,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>user_02920</t>
+          <t>user_02992</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>user_02591</t>
+          <t>user_02644</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -8205,12 +8205,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>user_02920</t>
+          <t>user_02992</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>user_02591</t>
+          <t>user_02644</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -8237,12 +8237,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>user_02920</t>
+          <t>user_02992</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>user_02591</t>
+          <t>user_02644</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -8269,12 +8269,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>user_02920</t>
+          <t>user_02992</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>user_02591</t>
+          <t>user_02644</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -8301,12 +8301,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>user_02920</t>
+          <t>user_02992</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>user_02591</t>
+          <t>user_02644</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -8333,12 +8333,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>user_02920</t>
+          <t>user_02992</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>user_02591</t>
+          <t>user_02644</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -8366,12 +8366,12 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>user_02920</t>
+          <t>user_02992</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>user_02591</t>
+          <t>user_02644</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -8401,12 +8401,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>user_02920</t>
+          <t>user_02992</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>user_02591</t>
+          <t>user_02644</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -8433,12 +8433,12 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>user_02920</t>
+          <t>user_02992</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>user_02591</t>
+          <t>user_02644</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -8465,12 +8465,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>user_02920</t>
+          <t>user_02992</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>user_02591</t>
+          <t>user_02644</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -8498,12 +8498,12 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>user_02920</t>
+          <t>user_02992</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>user_02591</t>
+          <t>user_02644</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -8531,12 +8531,12 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>user_02920</t>
+          <t>user_02992</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>user_02591</t>
+          <t>user_02644</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -8564,12 +8564,12 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>user_02920</t>
+          <t>user_02992</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>user_02591</t>
+          <t>user_02644</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -8600,12 +8600,12 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>user_02920</t>
+          <t>user_02992</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>user_02591</t>
+          <t>user_02644</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -8632,12 +8632,12 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>user_02920</t>
+          <t>user_02992</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>user_02591</t>
+          <t>user_02644</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -8664,12 +8664,12 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>user_02920</t>
+          <t>user_02992</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>user_02591</t>
+          <t>user_02644</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -8696,12 +8696,12 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>user_02159</t>
+          <t>user_02184</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>user_00851</t>
+          <t>user_00864</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -8712,7 +8712,7 @@
       <c r="D239" t="inlineStr"/>
       <c r="E239" t="inlineStr">
         <is>
-          <t>user_02652</t>
+          <t>user_02711</t>
         </is>
       </c>
       <c r="F239" t="n">
@@ -8735,12 +8735,12 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>user_02958</t>
+          <t>user_03038</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>user_00918</t>
+          <t>user_00931</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -8751,7 +8751,7 @@
       <c r="D240" t="inlineStr"/>
       <c r="E240" t="inlineStr">
         <is>
-          <t>user_02652</t>
+          <t>user_02711</t>
         </is>
       </c>
       <c r="F240" t="n">
@@ -8775,12 +8775,12 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>user_02958</t>
+          <t>user_03038</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>user_00918</t>
+          <t>user_00931</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -8807,12 +8807,12 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>user_02958</t>
+          <t>user_03038</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>user_00918</t>
+          <t>user_00931</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -8839,12 +8839,12 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>user_02958</t>
+          <t>user_03038</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>user_00918</t>
+          <t>user_00931</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -8871,12 +8871,12 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>user_02958</t>
+          <t>user_03038</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>user_00918</t>
+          <t>user_00931</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -8903,12 +8903,12 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>user_02958</t>
+          <t>user_03038</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>user_00918</t>
+          <t>user_00931</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -8935,12 +8935,12 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>user_02958</t>
+          <t>user_03038</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>user_00918</t>
+          <t>user_00931</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -8967,12 +8967,12 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>user_02958</t>
+          <t>user_03038</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>user_00918</t>
+          <t>user_00931</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -8999,12 +8999,12 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>user_02958</t>
+          <t>user_03038</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>user_00918</t>
+          <t>user_00931</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -9032,12 +9032,12 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>user_02958</t>
+          <t>user_03038</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>user_00918</t>
+          <t>user_00931</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -9065,12 +9065,12 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>user_02958</t>
+          <t>user_03038</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>user_00918</t>
+          <t>user_00931</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -9097,12 +9097,12 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>user_02958</t>
+          <t>user_03038</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>user_00918</t>
+          <t>user_00931</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -9130,12 +9130,12 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>user_02958</t>
+          <t>user_03038</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>user_00918</t>
+          <t>user_00931</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -9163,12 +9163,12 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>user_02958</t>
+          <t>user_03038</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>user_00918</t>
+          <t>user_00931</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -9195,12 +9195,12 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>user_02958</t>
+          <t>user_03038</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>user_00918</t>
+          <t>user_00931</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -9227,12 +9227,12 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>user_02958</t>
+          <t>user_03038</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>user_00918</t>
+          <t>user_00931</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -9259,12 +9259,12 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>user_02958</t>
+          <t>user_03038</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>user_00918</t>
+          <t>user_00931</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -9291,12 +9291,12 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>user_02958</t>
+          <t>user_03038</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>user_00918</t>
+          <t>user_00931</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -9323,12 +9323,12 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>user_02958</t>
+          <t>user_03038</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>user_00918</t>
+          <t>user_00931</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -9355,12 +9355,12 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>user_02958</t>
+          <t>user_03038</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>user_00918</t>
+          <t>user_00931</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -9394,12 +9394,12 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>user_02958</t>
+          <t>user_03038</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>user_00918</t>
+          <t>user_00931</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -9426,12 +9426,12 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>user_02154</t>
+          <t>user_02178</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>user_02618</t>
+          <t>user_02674</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -9442,7 +9442,7 @@
       <c r="D261" t="inlineStr"/>
       <c r="E261" t="inlineStr">
         <is>
-          <t>user_02652</t>
+          <t>user_02711</t>
         </is>
       </c>
       <c r="F261" t="n">
@@ -9465,12 +9465,12 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>user_02154</t>
+          <t>user_02178</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>user_02618</t>
+          <t>user_02674</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -9498,12 +9498,12 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>user_02154</t>
+          <t>user_02178</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>user_02618</t>
+          <t>user_02674</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -9530,12 +9530,12 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>user_02154</t>
+          <t>user_02178</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>user_02618</t>
+          <t>user_02674</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -9562,12 +9562,12 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>user_02154</t>
+          <t>user_02178</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>user_02618</t>
+          <t>user_02674</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -9595,12 +9595,12 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>user_02154</t>
+          <t>user_02178</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>user_02618</t>
+          <t>user_02674</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -9627,12 +9627,12 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>user_02154</t>
+          <t>user_02178</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>user_02618</t>
+          <t>user_02674</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -9659,12 +9659,12 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>user_02154</t>
+          <t>user_02178</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>user_02618</t>
+          <t>user_02674</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -9691,12 +9691,12 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>user_02154</t>
+          <t>user_02178</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>user_02618</t>
+          <t>user_02674</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -9723,12 +9723,12 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>user_02154</t>
+          <t>user_02178</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>user_02618</t>
+          <t>user_02674</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -9755,12 +9755,12 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>user_02154</t>
+          <t>user_02178</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>user_02618</t>
+          <t>user_02674</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -9787,12 +9787,12 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>user_02154</t>
+          <t>user_02178</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>user_02618</t>
+          <t>user_02674</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -9819,12 +9819,12 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>user_02154</t>
+          <t>user_02178</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>user_02618</t>
+          <t>user_02674</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -9852,12 +9852,12 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>user_02154</t>
+          <t>user_02178</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>user_02618</t>
+          <t>user_02674</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -9885,12 +9885,12 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>user_02154</t>
+          <t>user_02178</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>user_02618</t>
+          <t>user_02674</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -9917,12 +9917,12 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>user_02154</t>
+          <t>user_02178</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>user_02618</t>
+          <t>user_02674</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -9950,12 +9950,12 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>user_02154</t>
+          <t>user_02178</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>user_02618</t>
+          <t>user_02674</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -9983,12 +9983,12 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>user_02154</t>
+          <t>user_02178</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>user_02618</t>
+          <t>user_02674</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -10016,12 +10016,12 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>user_02154</t>
+          <t>user_02178</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>user_02618</t>
+          <t>user_02674</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -10051,12 +10051,12 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>user_02971</t>
+          <t>user_03051</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>user_02545</t>
+          <t>user_02596</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -10067,7 +10067,7 @@
       <c r="D280" t="inlineStr"/>
       <c r="E280" t="inlineStr">
         <is>
-          <t>user_02652</t>
+          <t>user_02711</t>
         </is>
       </c>
       <c r="F280" t="n">
@@ -10095,12 +10095,12 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>user_02971</t>
+          <t>user_03051</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>user_02545</t>
+          <t>user_02596</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -10127,12 +10127,12 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>user_02971</t>
+          <t>user_03051</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>user_02545</t>
+          <t>user_02596</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -10159,12 +10159,12 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>user_02971</t>
+          <t>user_03051</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>user_02545</t>
+          <t>user_02596</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -10195,12 +10195,12 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>user_02971</t>
+          <t>user_03051</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>user_02545</t>
+          <t>user_02596</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -10227,12 +10227,12 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>user_02971</t>
+          <t>user_03051</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>user_02545</t>
+          <t>user_02596</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -10260,12 +10260,12 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>user_02971</t>
+          <t>user_03051</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>user_02545</t>
+          <t>user_02596</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -10293,12 +10293,12 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>user_02971</t>
+          <t>user_03051</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>user_02545</t>
+          <t>user_02596</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -10325,12 +10325,12 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>user_02971</t>
+          <t>user_03051</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>user_02545</t>
+          <t>user_02596</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -10357,12 +10357,12 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>user_02971</t>
+          <t>user_03051</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>user_02545</t>
+          <t>user_02596</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -10389,12 +10389,12 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>user_02971</t>
+          <t>user_03051</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>user_02545</t>
+          <t>user_02596</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -10421,12 +10421,12 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>user_02971</t>
+          <t>user_03051</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>user_02545</t>
+          <t>user_02596</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -10454,12 +10454,12 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>user_02971</t>
+          <t>user_03051</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>user_02545</t>
+          <t>user_02596</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -10488,12 +10488,12 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>user_02971</t>
+          <t>user_03051</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>user_02545</t>
+          <t>user_02596</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -10520,12 +10520,12 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>user_02971</t>
+          <t>user_03051</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>user_02545</t>
+          <t>user_02596</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -10555,12 +10555,12 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>user_02971</t>
+          <t>user_03051</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>user_02545</t>
+          <t>user_02596</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -10587,12 +10587,12 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>user_02971</t>
+          <t>user_03051</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>user_02545</t>
+          <t>user_02596</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -10620,12 +10620,12 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>user_02971</t>
+          <t>user_03051</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>user_02545</t>
+          <t>user_02596</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -10652,12 +10652,12 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>user_02971</t>
+          <t>user_03051</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>user_02545</t>
+          <t>user_02596</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -10685,12 +10685,12 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>user_02971</t>
+          <t>user_03051</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>user_02545</t>
+          <t>user_02596</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -10717,12 +10717,12 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>user_02971</t>
+          <t>user_03051</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>user_02545</t>
+          <t>user_02596</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -10749,12 +10749,12 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>user_02922</t>
+          <t>user_02995</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>user_02817</t>
+          <t>user_02882</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -10765,7 +10765,7 @@
       <c r="D301" t="inlineStr"/>
       <c r="E301" t="inlineStr">
         <is>
-          <t>user_02652</t>
+          <t>user_02711</t>
         </is>
       </c>
       <c r="F301" t="n">
@@ -10790,12 +10790,12 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>user_02922</t>
+          <t>user_02995</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>user_02817</t>
+          <t>user_02882</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -10826,12 +10826,12 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>user_02922</t>
+          <t>user_02995</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>user_02817</t>
+          <t>user_02882</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -10858,12 +10858,12 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>user_02922</t>
+          <t>user_02995</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>user_02817</t>
+          <t>user_02882</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -10890,12 +10890,12 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>user_02922</t>
+          <t>user_02995</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>user_02817</t>
+          <t>user_02882</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -10923,12 +10923,12 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>user_02922</t>
+          <t>user_02995</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>user_02817</t>
+          <t>user_02882</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -10956,12 +10956,12 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>user_02922</t>
+          <t>user_02995</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>user_02817</t>
+          <t>user_02882</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -10989,12 +10989,12 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>user_02922</t>
+          <t>user_02995</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>user_02817</t>
+          <t>user_02882</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -11029,12 +11029,12 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>user_02922</t>
+          <t>user_02995</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>user_02817</t>
+          <t>user_02882</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -11062,12 +11062,12 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>user_02922</t>
+          <t>user_02995</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>user_02817</t>
+          <t>user_02882</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -11098,12 +11098,12 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>user_02922</t>
+          <t>user_02995</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>user_02817</t>
+          <t>user_02882</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -11132,12 +11132,12 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>user_02922</t>
+          <t>user_02995</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>user_02817</t>
+          <t>user_02882</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -11166,12 +11166,12 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>user_02922</t>
+          <t>user_02995</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>user_02817</t>
+          <t>user_02882</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -11198,12 +11198,12 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>user_02922</t>
+          <t>user_02995</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>user_02817</t>
+          <t>user_02882</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -11231,12 +11231,12 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>user_02922</t>
+          <t>user_02995</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>user_02817</t>
+          <t>user_02882</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -11265,12 +11265,12 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>user_02922</t>
+          <t>user_02995</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>user_02817</t>
+          <t>user_02882</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -11297,12 +11297,12 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>user_02922</t>
+          <t>user_02995</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>user_02817</t>
+          <t>user_02882</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -11329,12 +11329,12 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>user_02922</t>
+          <t>user_02995</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>user_02817</t>
+          <t>user_02882</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -11361,12 +11361,12 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>user_02922</t>
+          <t>user_02995</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>user_02817</t>
+          <t>user_02882</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -11393,12 +11393,12 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>user_00904</t>
+          <t>user_00917</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>user_00868</t>
+          <t>user_00881</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -11409,7 +11409,7 @@
       <c r="D320" t="inlineStr"/>
       <c r="E320" t="inlineStr">
         <is>
-          <t>user_02652</t>
+          <t>user_02711</t>
         </is>
       </c>
       <c r="F320" t="n">
@@ -11434,12 +11434,12 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>user_00904</t>
+          <t>user_00917</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>user_00868</t>
+          <t>user_00881</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -11468,12 +11468,12 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>user_00904</t>
+          <t>user_00917</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>user_00868</t>
+          <t>user_00881</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -11500,12 +11500,12 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>user_00904</t>
+          <t>user_00917</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>user_00868</t>
+          <t>user_00881</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -11533,12 +11533,12 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>user_00904</t>
+          <t>user_00917</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>user_00868</t>
+          <t>user_00881</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -11565,12 +11565,12 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>user_00904</t>
+          <t>user_00917</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>user_00868</t>
+          <t>user_00881</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -11599,12 +11599,12 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>user_00904</t>
+          <t>user_00917</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>user_00868</t>
+          <t>user_00881</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -11634,12 +11634,12 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>user_00904</t>
+          <t>user_00917</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>user_00868</t>
+          <t>user_00881</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -11667,12 +11667,12 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>user_00904</t>
+          <t>user_00917</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>user_00868</t>
+          <t>user_00881</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -11703,12 +11703,12 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>user_00904</t>
+          <t>user_00917</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>user_00868</t>
+          <t>user_00881</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -11735,12 +11735,12 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>user_00904</t>
+          <t>user_00917</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>user_00868</t>
+          <t>user_00881</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -11772,12 +11772,12 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>user_00904</t>
+          <t>user_00917</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>user_00868</t>
+          <t>user_00881</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -11804,12 +11804,12 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>user_00904</t>
+          <t>user_00917</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>user_00868</t>
+          <t>user_00881</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -11836,12 +11836,12 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>user_00904</t>
+          <t>user_00917</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>user_00868</t>
+          <t>user_00881</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -11869,12 +11869,12 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>user_00904</t>
+          <t>user_00917</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>user_00868</t>
+          <t>user_00881</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -11905,12 +11905,12 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>user_00904</t>
+          <t>user_00917</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>user_00868</t>
+          <t>user_00881</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -11938,12 +11938,12 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>user_00904</t>
+          <t>user_00917</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>user_00868</t>
+          <t>user_00881</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -11970,12 +11970,12 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>user_00904</t>
+          <t>user_00917</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>user_00868</t>
+          <t>user_00881</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -12003,12 +12003,12 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>user_00904</t>
+          <t>user_00917</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>user_00868</t>
+          <t>user_00881</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -12039,12 +12039,12 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>user_00904</t>
+          <t>user_00917</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>user_00868</t>
+          <t>user_00881</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -12074,12 +12074,12 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>user_00904</t>
+          <t>user_00917</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>user_00868</t>
+          <t>user_00881</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -12107,12 +12107,12 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>user_00904</t>
+          <t>user_00917</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>user_00868</t>
+          <t>user_00881</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -12139,12 +12139,12 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>user_02921</t>
+          <t>user_02994</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>user_02830</t>
+          <t>user_02896</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -12155,7 +12155,7 @@
       <c r="D342" t="inlineStr"/>
       <c r="E342" t="inlineStr">
         <is>
-          <t>user_02652</t>
+          <t>user_02711</t>
         </is>
       </c>
       <c r="F342" t="n">
@@ -12179,12 +12179,12 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>user_02921</t>
+          <t>user_02994</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>user_02830</t>
+          <t>user_02896</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -12211,12 +12211,12 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>user_02921</t>
+          <t>user_02994</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>user_02830</t>
+          <t>user_02896</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -12243,12 +12243,12 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>user_02921</t>
+          <t>user_02994</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>user_02830</t>
+          <t>user_02896</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -12287,12 +12287,12 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>user_02921</t>
+          <t>user_02994</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>user_02830</t>
+          <t>user_02896</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -12332,12 +12332,12 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>user_02921</t>
+          <t>user_02994</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>user_02830</t>
+          <t>user_02896</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -12364,12 +12364,12 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>user_02921</t>
+          <t>user_02994</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>user_02830</t>
+          <t>user_02896</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -12396,12 +12396,12 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>user_02921</t>
+          <t>user_02994</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>user_02830</t>
+          <t>user_02896</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -12428,12 +12428,12 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>user_02921</t>
+          <t>user_02994</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>user_02830</t>
+          <t>user_02896</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -12461,12 +12461,12 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>user_02921</t>
+          <t>user_02994</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>user_02830</t>
+          <t>user_02896</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -12493,12 +12493,12 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>user_02921</t>
+          <t>user_02994</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>user_02830</t>
+          <t>user_02896</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -12525,12 +12525,12 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>user_02921</t>
+          <t>user_02994</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>user_02830</t>
+          <t>user_02896</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -12557,12 +12557,12 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>user_02921</t>
+          <t>user_02994</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>user_02830</t>
+          <t>user_02896</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -12589,12 +12589,12 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>user_02921</t>
+          <t>user_02994</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>user_02830</t>
+          <t>user_02896</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -12621,12 +12621,12 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>user_02921</t>
+          <t>user_02994</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>user_02830</t>
+          <t>user_02896</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -12653,12 +12653,12 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>user_02921</t>
+          <t>user_02994</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>user_02830</t>
+          <t>user_02896</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -12685,12 +12685,12 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>user_02921</t>
+          <t>user_02994</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>user_02830</t>
+          <t>user_02896</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -12719,12 +12719,12 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>user_02921</t>
+          <t>user_02994</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>user_02830</t>
+          <t>user_02896</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -12751,12 +12751,12 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>user_02921</t>
+          <t>user_02994</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>user_02830</t>
+          <t>user_02896</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -12783,12 +12783,12 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>user_02921</t>
+          <t>user_02994</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>user_02830</t>
+          <t>user_02896</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -12816,12 +12816,12 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>user_02921</t>
+          <t>user_02994</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>user_02830</t>
+          <t>user_02896</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -12848,12 +12848,12 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>user_02921</t>
+          <t>user_02994</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>user_02830</t>
+          <t>user_02896</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -12885,7 +12885,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>user_02546</t>
+          <t>user_02597</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -12896,7 +12896,7 @@
       <c r="D364" t="inlineStr"/>
       <c r="E364" t="inlineStr">
         <is>
-          <t>user_02652</t>
+          <t>user_02711</t>
         </is>
       </c>
       <c r="F364" t="n">
@@ -12924,7 +12924,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>user_02546</t>
+          <t>user_02597</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -12956,7 +12956,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>user_02546</t>
+          <t>user_02597</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -12988,7 +12988,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>user_02546</t>
+          <t>user_02597</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -13021,7 +13021,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>user_02546</t>
+          <t>user_02597</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -13055,7 +13055,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>user_02546</t>
+          <t>user_02597</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -13088,7 +13088,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>user_02546</t>
+          <t>user_02597</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -13123,7 +13123,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>user_02546</t>
+          <t>user_02597</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -13157,7 +13157,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>user_02546</t>
+          <t>user_02597</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -13190,7 +13190,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>user_02546</t>
+          <t>user_02597</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -13223,7 +13223,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>user_02546</t>
+          <t>user_02597</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -13251,12 +13251,12 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>user_01517</t>
+          <t>user_01538</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>user_00952</t>
+          <t>user_00965</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -13267,7 +13267,7 @@
       <c r="D375" t="inlineStr"/>
       <c r="E375" t="inlineStr">
         <is>
-          <t>user_02652</t>
+          <t>user_02711</t>
         </is>
       </c>
       <c r="F375" t="n">
@@ -13289,12 +13289,12 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>user_01517</t>
+          <t>user_01538</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>user_00952</t>
+          <t>user_00965</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -13321,12 +13321,12 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>user_01517</t>
+          <t>user_01538</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>user_00952</t>
+          <t>user_00965</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -13357,12 +13357,12 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>user_01517</t>
+          <t>user_01538</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>user_00952</t>
+          <t>user_00965</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -13393,12 +13393,12 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>user_01517</t>
+          <t>user_01538</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>user_00952</t>
+          <t>user_00965</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -13431,12 +13431,12 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>user_01517</t>
+          <t>user_01538</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>user_00952</t>
+          <t>user_00965</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -13464,12 +13464,12 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>user_01517</t>
+          <t>user_01538</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>user_00952</t>
+          <t>user_00965</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -13496,12 +13496,12 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>user_01517</t>
+          <t>user_01538</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>user_00952</t>
+          <t>user_00965</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -13529,12 +13529,12 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>user_01517</t>
+          <t>user_01538</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>user_00952</t>
+          <t>user_00965</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -13561,12 +13561,12 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>user_01517</t>
+          <t>user_01538</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>user_00952</t>
+          <t>user_00965</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -13593,12 +13593,12 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>user_01517</t>
+          <t>user_01538</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>user_00952</t>
+          <t>user_00965</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -13625,12 +13625,12 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>user_01517</t>
+          <t>user_01538</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>user_00952</t>
+          <t>user_00965</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -13657,12 +13657,12 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>user_01517</t>
+          <t>user_01538</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>user_00952</t>
+          <t>user_00965</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -13689,12 +13689,12 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>user_01517</t>
+          <t>user_01538</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>user_00952</t>
+          <t>user_00965</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -13721,12 +13721,12 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>user_01517</t>
+          <t>user_01538</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>user_00952</t>
+          <t>user_00965</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -13756,12 +13756,12 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>user_01517</t>
+          <t>user_01538</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>user_00952</t>
+          <t>user_00965</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -13788,12 +13788,12 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>user_01517</t>
+          <t>user_01538</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>user_00952</t>
+          <t>user_00965</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -13820,12 +13820,12 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>user_01517</t>
+          <t>user_01538</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>user_00952</t>
+          <t>user_00965</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -13853,12 +13853,12 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>user_01517</t>
+          <t>user_01538</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>user_00952</t>
+          <t>user_00965</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -13885,12 +13885,12 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>user_01517</t>
+          <t>user_01538</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>user_00952</t>
+          <t>user_00965</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -13917,12 +13917,12 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>user_01517</t>
+          <t>user_01538</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>user_00952</t>
+          <t>user_00965</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -13949,12 +13949,12 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>user_01529</t>
+          <t>user_01550</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>user_01526</t>
+          <t>user_01547</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -13989,12 +13989,12 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>user_01529</t>
+          <t>user_01550</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>user_01526</t>
+          <t>user_01547</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -14031,12 +14031,12 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>user_01529</t>
+          <t>user_01550</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>user_01526</t>
+          <t>user_01547</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -14071,12 +14071,12 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>user_01529</t>
+          <t>user_01550</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>user_01526</t>
+          <t>user_01547</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -14111,12 +14111,12 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>user_01529</t>
+          <t>user_01550</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>user_01526</t>
+          <t>user_01547</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -14152,12 +14152,12 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>user_01529</t>
+          <t>user_01550</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>user_01526</t>
+          <t>user_01547</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">

--- a/#Hearts2Hearts_anonymized.xlsx
+++ b/#Hearts2Hearts_anonymized.xlsx
@@ -518,7 +518,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -602,7 +602,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -818,7 +818,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -862,7 +862,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -994,7 +994,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1261,7 +1261,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7329,7 +7329,7 @@
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7372,7 +7372,7 @@
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7415,7 +7415,7 @@
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7462,7 +7462,7 @@
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7551,7 +7551,7 @@
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13982,7 +13982,7 @@
       </c>
       <c r="J396" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14024,7 +14024,7 @@
       </c>
       <c r="J397" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14064,7 +14064,7 @@
       </c>
       <c r="J398" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14104,7 +14104,7 @@
       </c>
       <c r="J399" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14145,7 +14145,7 @@
       </c>
       <c r="J400" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14185,7 +14185,7 @@
       </c>
       <c r="J401" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
